--- a/liq_calc/output/lcr_nsfr_report.xlsx
+++ b/liq_calc/output/lcr_nsfr_report.xlsx
@@ -482,28 +482,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3400000000</v>
+        <v>3000000000</v>
       </c>
       <c r="D2" t="n">
-        <v>1437463075</v>
+        <v>1321948840</v>
       </c>
       <c r="E2" t="n">
-        <v>66472976.47499999</v>
+        <v>64568617.88250001</v>
       </c>
       <c r="F2" t="n">
-        <v>1370990098.525</v>
+        <v>1257380222.1175</v>
       </c>
       <c r="G2" t="n">
-        <v>2.479959558904138</v>
+        <v>2.38591314483047</v>
       </c>
       <c r="H2" t="n">
-        <v>8600000000</v>
+        <v>8620000000</v>
       </c>
       <c r="I2" t="n">
-        <v>4880000000</v>
+        <v>5320000000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.762295081967213</v>
+        <v>1.620300751879699</v>
       </c>
     </row>
   </sheetData>

--- a/liq_calc/output/lcr_nsfr_report.xlsx
+++ b/liq_calc/output/lcr_nsfr_report.xlsx
@@ -485,16 +485,16 @@
         <v>3000000000</v>
       </c>
       <c r="D2" t="n">
-        <v>1321948840</v>
+        <v>1320960080</v>
       </c>
       <c r="E2" t="n">
-        <v>64568617.88250001</v>
+        <v>65531386.0575</v>
       </c>
       <c r="F2" t="n">
-        <v>1257380222.1175</v>
+        <v>1255428693.9425</v>
       </c>
       <c r="G2" t="n">
-        <v>2.38591314483047</v>
+        <v>2.389621978910578</v>
       </c>
       <c r="H2" t="n">
         <v>8620000000</v>

--- a/liq_calc/output/lcr_nsfr_report.xlsx
+++ b/liq_calc/output/lcr_nsfr_report.xlsx
@@ -485,25 +485,25 @@
         <v>3000000000</v>
       </c>
       <c r="D2" t="n">
-        <v>1320960080</v>
+        <v>1307749125</v>
       </c>
       <c r="E2" t="n">
-        <v>65531386.0575</v>
+        <v>226071911.19</v>
       </c>
       <c r="F2" t="n">
-        <v>1255428693.9425</v>
+        <v>1081677213.81</v>
       </c>
       <c r="G2" t="n">
-        <v>2.389621978910578</v>
+        <v>2.773470645122566</v>
       </c>
       <c r="H2" t="n">
-        <v>8620000000</v>
+        <v>8560000000</v>
       </c>
       <c r="I2" t="n">
         <v>5320000000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.620300751879699</v>
+        <v>1.609022556390977</v>
       </c>
     </row>
   </sheetData>

--- a/liq_calc/output/lcr_nsfr_report.xlsx
+++ b/liq_calc/output/lcr_nsfr_report.xlsx
@@ -485,16 +485,16 @@
         <v>3000000000</v>
       </c>
       <c r="D2" t="n">
-        <v>1307749125</v>
+        <v>1345375731.818182</v>
       </c>
       <c r="E2" t="n">
-        <v>226071911.19</v>
+        <v>521295730.8</v>
       </c>
       <c r="F2" t="n">
-        <v>1081677213.81</v>
+        <v>824080001.0181818</v>
       </c>
       <c r="G2" t="n">
-        <v>2.773470645122566</v>
+        <v>3.640423255379802</v>
       </c>
       <c r="H2" t="n">
         <v>8560000000</v>

--- a/liq_calc/output/lcr_nsfr_report.xlsx
+++ b/liq_calc/output/lcr_nsfr_report.xlsx
@@ -474,7 +474,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>46203</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -485,16 +485,16 @@
         <v>3000000000</v>
       </c>
       <c r="D2" t="n">
-        <v>1345375731.818182</v>
+        <v>1398721513.636364</v>
       </c>
       <c r="E2" t="n">
-        <v>521295730.8</v>
+        <v>387957125.6775</v>
       </c>
       <c r="F2" t="n">
-        <v>824080001.0181818</v>
+        <v>1010764387.958863</v>
       </c>
       <c r="G2" t="n">
-        <v>3.640423255379802</v>
+        <v>2.968050750242791</v>
       </c>
       <c r="H2" t="n">
         <v>8560000000</v>

--- a/liq_calc/output/lcr_nsfr_report.xlsx
+++ b/liq_calc/output/lcr_nsfr_report.xlsx
@@ -485,25 +485,25 @@
         <v>3000000000</v>
       </c>
       <c r="D2" t="n">
-        <v>1398721513.636364</v>
+        <v>1459654980</v>
       </c>
       <c r="E2" t="n">
-        <v>387957125.6775</v>
+        <v>386967946.83</v>
       </c>
       <c r="F2" t="n">
-        <v>1010764387.958863</v>
+        <v>1072687033.17</v>
       </c>
       <c r="G2" t="n">
-        <v>2.968050750242791</v>
+        <v>2.796715078334091</v>
       </c>
       <c r="H2" t="n">
-        <v>8560000000</v>
+        <v>8590000000</v>
       </c>
       <c r="I2" t="n">
         <v>5320000000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.609022556390977</v>
+        <v>1.614661654135338</v>
       </c>
     </row>
   </sheetData>
